--- a/data_extactor/batch_10_fa/trimmed/batch_0021_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0021_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | ریاضیات | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | ریاضیات | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | مکانیک | رایانه و الکترونیک | ریاضیات | فیزیک | ترابری و حمل‌ونقل | طراحی</t>
+          <t>مهندسی و فناوری | مکانیک | رایانه و الکترونیک | ریاضیات | فیزیک | حمل و نقل | طراحی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | حساسیت به مسئله | دید نزدیک | استدلال استقرایی | درک شفاهی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | استدلال قیاسی | حساسیت به مسئله | بینایی نزدیک | استدلال استقرایی | درک شفاهی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مهندسان خودرو | تکنسین‌ها و مکانیک‌های تعمیر و خدمات خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌ها و کارشناسان فنی مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان فنی الکترومکانیک و مکاترونیک | تکنسین‌ها و کارشناسان فنی مهندسی مکانیک | مهندسان مکانیک</t>
+          <t>مهندسان خودرو | مکانیک و تکنسین خدمات خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | فیزیک | مکانیک | تولید و فراوری</t>
+          <t>ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | فیزیک | مکانیک | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌های مهندسی خودرو | تکنسین‌های شیمی | تکنسین‌ها و کارشناسان فنی مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان فنی الکترومکانیک و مکاترونیک | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | تکنسین‌ها و کارشناسان فنی مهندسی مکانیک | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>تکنسین‌های مهندسی خودرو | تکنسین‌های شیمی | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | دید نزدیک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فنی مهندسی عمران | تکنسین‌ها و کارشناسان فنی مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان فنی مهندسی مکانیک | تکنسین‌ها و کارشناسان فنی مهندسی صنایع | تکنسین‌ها و کارشناسان فنی مهندسی محیط زیست | تکنسین‌ها و کارشناسان فنی الکترومکانیک و مکاترونیک | تکنسین‌ها و کارشناسان فنی کالیبراسیون</t>
+          <t>کارشناسان و تکنسین‌های مهندسی عمران | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی مکانیک | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی محیط زیست | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | تکنسین‌ها و کارشناسان فنی کالیبراسیون</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری | سخن گفتن | ریاضیات | علوم تجربی</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری | سخن گفتن | ریاضیات | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | فیزیک | رایانه و الکترونیک | تولید و فراوری | مکانیک | ایمنی و امنیت عمومی</t>
+          <t>مهندسی و فناوری | ریاضیات | فیزیک | رایانه و الکترونیک | تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک کتبی | استدلال قیاسی | درک شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک کتبی | استدلال قیاسی | درک شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌ها و کارشناسان فنی مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان فنی مهندسی صنایع | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | تکنسین‌ها و کارشناسان فنی مهندسی مکانیک | تکنسین‌های پایش پرتوی و هسته‌ای | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی صنایع | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارشناسان و تکنسین‌های مهندسی مکانیک | تکنسین‌های پایش و حفاظت پرتوی | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | مکانیک | تولید و فراوری | فیزیک</t>
+          <t>مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | مکانیک | تولید و فرآوری | فیزیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | حساسیت به مسئله | درک کتبی | مرتب‌سازی اطلاعات | چابکی انگشتان | استدلال قیاسی</t>
+          <t>بینایی نزدیک | درک شفاهی | حساسیت به مسئله | درک کتبی | ترتیب‌دهی اطلاعات | مهارت انگشتان | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان برق | تکنسین‌ها و کارشناسان فنی مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان فنی الکترومکانیک و مکاترونیک | تکنسین‌ها و کارشناسان فنی مهندسی مکانیک | تکنسین‌های آزمایشگاه عینک‌سازی و اپتیک | مهندسان فوتونیک</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | کارشناسان و تکنسین‌های مهندسی مکانیک | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | مهندسان فوتونیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نگارش | ریاضیات | نظارت | شنیدن فعال | سخن گفتن | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | ریاضیات | نظارت | گوش دادن فعال | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | جغرافیا | ریاضیات | زبان انگلیسی | مهندسی و فناوری | طراحی | خدمات مشتریان و خدمات فردی</t>
+          <t>رایانه و الکترونیک | جغرافیا | ریاضیات | زبان انگلیسی | مهندسی و فناوری | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک کتبی | دید نزدیک | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی</t>
+          <t>درک کتبی | بینایی نزدیک | استدلال استقرایی | بیان شفاهی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | نقشه‌نگاران و متخصصان فتوگرامتری | تکنسین‌ها و کارشناسان فنی مهندسی عمران | مهندسان عمران | نقشه‌برداران ژئودزی | تکنسین‌ها و کارشناسان فنی سامانه‌های اطلاعات جغرافیایی GIS | نقشه‌برداران</t>
+          <t>نقشه‌کشان معماری و عمران | کارشناسان نقشه‌نگاری و فتوگرامتری | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مهندسان نقشه‌برداری ژئودزی | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | مهندسان نقشه‌برداری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | علوم تجربی | نگارش | تفکر انتقادی | یادگیری فعال | شنیدن فعال | سخن گفتن | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>درک مطلب | علوم | نگارش | تفکر انتقادی | یادگیری فعال | گوش دادن فعال | سخن گفتن | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | ریاضیات | شیمی | تولیدات کشاورزی و دامی | آموزش و تدریس | رایانه و الکترونیک</t>
+          <t>زیست‌شناسی | ریاضیات | شیمی | تولید مواد غذایی | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی و دامپروری | اصلاح‌کنندگان نژاد دام و حیوانات | زیست‌شناسان | مدیران مزارع، دامداری‌ها و سایر واحدهای کشاورزی | متخصصان ژنتیک | دامپزشکان | تکنسین‌ها و کارشناسان فنی دامپزشکی</t>
+          <t>تکنسین‌های کشاورزی | تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | زیست‌شناسان | مدیران امور کشاورزی، دامپروری و شیلات | متخصصان ژنتیک | دامپزشکان | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | علوم تجربی | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>یادگیری فعال | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | علوم | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فراوری | تولیدات کشاورزی و دامی | شیمی | ریاضیات | مهندسی و فناوری | زیست‌شناسی | حقوق و مقررات دولتی</t>
+          <t>تولید و فرآوری | تولید مواد غذایی | شیمی | ریاضیات | مهندسی و فناوری | زیست‌شناسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | تکنسین‌های صنایع غذایی | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | میکروبیولوژیست‌ها | کارشناسان کنترل کیفیت</t>
+          <t>مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | تکنسین‌های علوم و صنایع غذایی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | میکروبیولوژیست‌ها | کارشناسان تحلیل کنترل کیفیت</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | یادگیری فعال | تفکر انتقادی | علوم تجربی | شنیدن فعال | نگارش | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | یادگیری فعال | تفکر انتقادی | علوم | گوش دادن فعال | نگارش | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی و دامپروری | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | کارگران زراعت، باغبانی، نهالستان و گلخانه | میکروبیولوژیست‌ها | تکنسین‌های کشاورزی دقیق</t>
+          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | کارگران زراعت، نهالستان و گلخانه | میکروبیولوژیست‌ها | تکنسین‌های کشاورزی دقیق</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>علوم تجربی | درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | شنیدن فعال | راهبردهای یادگیری | ریاضیات | نظارت</t>
+          <t>علوم | درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | گوش دادن فعال | راهبردهای یادگیری | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | زیست‌شناسان | شیمی‌دانان | متخصصان ژنتیک | دانشمندان علوم پزشکی، به‌جز اپیدمیولوژیست‌ها | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی</t>
+          <t>تکنسین‌های علوم زیستی | زیست‌شناسان | شیمی‌دانان | متخصصان ژنتیک | پژوهشگران و دانشمندان علوم پزشکی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
